--- a/tools/importer/reports/import-faq.report.xlsx
+++ b/tools/importer/reports/import-faq.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="105">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,6 +19,12 @@
     <t>blocks</t>
   </si>
   <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>errorStack</t>
+  </si>
+  <si>
     <t>path</t>
   </si>
   <si>
@@ -40,280 +46,289 @@
     <t>about-us.report.json</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>CustomImportScript.default not found after 10s. The bundled script may not have loaded correctly. Check browser console for errors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: CustomImportScript.default not found after 10s. The bundled script may not have loaded correctly. Check browser console for errors.
+    at processUrl (file:///home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:662:13)
+    at runNextTicks (node:internal/process/task_queues:65:5)
+    at process.processImmediate (node:internal/timers:472:9)
+    at async main (file:///home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:954:22)</t>
+  </si>
+  <si>
+    <t>about-us</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>2026-09-03T08:28:47.347Z</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/about-us</t>
+  </si>
+  <si>
+    <t>blog.report.json</t>
+  </si>
+  <si>
+    <t>["columns-feature","columns-feature","cards-media"]</t>
+  </si>
+  <si>
+    <t>blog</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>article-index</t>
+  </si>
+  <si>
+    <t>2026-09-03T06:22:30.462Z</t>
+  </si>
+  <si>
+    <t>Blog — WKND Trendsetters</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/blog</t>
+  </si>
+  <si>
+    <t>case-studies.report.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: CustomImportScript.default not found after 10s. The bundled script may not have loaded correctly. Check browser console for errors.
+    at processUrl (file:///home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:662:13)
+    at async main (file:///home/node/.excat-marketplaces/excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:954:22)</t>
+  </si>
+  <si>
+    <t>case-studies</t>
+  </si>
+  <si>
+    <t>2026-09-03T08:29:22.607Z</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/case-studies</t>
+  </si>
+  <si>
+    <t>faq.report.json</t>
+  </si>
+  <si>
+    <t>faq</t>
+  </si>
+  <si>
+    <t>2026-09-03T08:30:40.568Z</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/faq</t>
+  </si>
+  <si>
+    <t>fashion-insights.report.json</t>
+  </si>
+  <si>
+    <t>["columns-feature","columns-feature","cards-media","cards-media"]</t>
+  </si>
+  <si>
+    <t>fashion-insights</t>
+  </si>
+  <si>
+    <t>2026-09-03T06:22:34.182Z</t>
+  </si>
+  <si>
+    <t>Fashion Blog - Discover Trends in Young Fashion</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/fashion-insights</t>
+  </si>
+  <si>
+    <t>fashion-trends-of-the-season.report.json</t>
+  </si>
+  <si>
+    <t>fashion-trends-of-the-season</t>
+  </si>
+  <si>
+    <t>trends-landing</t>
+  </si>
+  <si>
+    <t>2026-09-03T06:26:00.356Z</t>
+  </si>
+  <si>
+    <t>Top Fashion Trends for Young People | Fashion Blog</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/fashion-trends-of-the-season</t>
+  </si>
+  <si>
+    <t>fashion-trends-young-adults-casual-sport.report.json</t>
+  </si>
+  <si>
+    <t>fashion-trends-young-adults-casual-sport</t>
+  </si>
+  <si>
+    <t>2026-09-02T18:07:04.572Z</t>
+  </si>
+  <si>
+    <t>Fashion Trends for Young Adults | Fashion Blog</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/fashion-trends-young-adults-casual-sport</t>
+  </si>
+  <si>
+    <t>fashion-trends-young-adults.report.json</t>
+  </si>
+  <si>
+    <t>["columns-feature","cards-media","cards-media","cards-media"]</t>
+  </si>
+  <si>
+    <t>fashion-trends-young-adults</t>
+  </si>
+  <si>
+    <t>2026-09-03T06:25:55.156Z</t>
+  </si>
+  <si>
+    <t>Fashion Trends for Young Adults - Fashion Blog</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/fashion-trends-young-adults</t>
+  </si>
+  <si>
+    <t>index.report.json</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>2026-09-03T08:29:57.137Z</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/</t>
+  </si>
+  <si>
+    <t>blog/ace-pro-court-polo.report.json</t>
+  </si>
+  <si>
+    <t>["columns-article","table-spec"]</t>
+  </si>
+  <si>
+    <t>blog/ace-pro-court-polo</t>
+  </si>
+  <si>
+    <t>2026-09-02T08:57:44.303Z</t>
+  </si>
+  <si>
+    <t>Court cool, street ready — the Ace Pro polo | Fashion Blog</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/blog/ace-pro-court-polo</t>
+  </si>
+  <si>
+    <t>blog/fashion-blog-post.report.json</t>
+  </si>
+  <si>
+    <t>["columns-article"]</t>
+  </si>
+  <si>
+    <t>blog/fashion-blog-post</t>
+  </si>
+  <si>
+    <t>2026-09-02T17:33:14.871Z</t>
+  </si>
+  <si>
+    <t>Game on, style up | Fashion Blog</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/blog/fashion-blog-post</t>
+  </si>
+  <si>
+    <t>blog/fashion-trends-young-culture.report.json</t>
+  </si>
+  <si>
+    <t>blog/fashion-trends-young-culture</t>
+  </si>
+  <si>
+    <t>2026-09-02T17:33:05.631Z</t>
+  </si>
+  <si>
+    <t>Sunkissed and effortless | Fashion Blog</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/blog/fashion-trends-young-culture</t>
+  </si>
+  <si>
+    <t>blog/fashion-trends-young-style.report.json</t>
+  </si>
+  <si>
+    <t>blog/fashion-trends-young-style</t>
+  </si>
+  <si>
+    <t>2026-09-02T17:33:10.033Z</t>
+  </si>
+  <si>
+    <t>Party fits that pop | Fashion Blog</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/blog/fashion-trends-young-style</t>
+  </si>
+  <si>
+    <t>blog/flip-flop-summer-style.report.json</t>
+  </si>
+  <si>
+    <t>blog/flip-flop-summer-style</t>
+  </si>
+  <si>
+    <t>2026-09-02T17:32:56.858Z</t>
+  </si>
+  <si>
+    <t>Slide into summer — flip flops that serve | Fashion Blog</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/blog/flip-flop-summer-style</t>
+  </si>
+  <si>
+    <t>blog/latest-trends-young-casual-fashion.report.json</t>
+  </si>
+  <si>
+    <t>blog/latest-trends-young-casual-fashion</t>
+  </si>
+  <si>
+    <t>2026-09-02T17:33:01.572Z</t>
+  </si>
+  <si>
+    <t>Tennis style, redefined | Fashion Blog</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/blog/latest-trends-young-casual-fashion</t>
+  </si>
+  <si>
+    <t>blog/street-style-trends.report.json</t>
+  </si>
+  <si>
+    <t>blog/street-style-trends</t>
+  </si>
+  <si>
+    <t>2026-09-02T17:33:19.128Z</t>
+  </si>
+  <si>
+    <t>Street style, your way | Fashion Blog</t>
+  </si>
+  <si>
+    <t>https://wknd-trendsetters.site/blog/street-style-trends</t>
+  </si>
+  <si>
+    <t>magazine/article-1.report.json</t>
+  </si>
+  <si>
     <t>["columns-feature","columns-feature","cards-media","cards-media","tabs-profile","accordion-faq","hero-overlay"]</t>
   </si>
   <si>
-    <t>about-us</t>
-  </si>
-  <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>2026-09-02T09:28:43.805Z</t>
+    <t>magazine/article-1</t>
+  </si>
+  <si>
+    <t>2026-09-02T06:50:43.262Z</t>
   </si>
   <si>
     <t>WKND Trendsetters - Fresh Looks, Bold Stories, Real Life</t>
-  </si>
-  <si>
-    <t>https://wknd-trendsetters.site/about-us</t>
-  </si>
-  <si>
-    <t>blog.report.json</t>
-  </si>
-  <si>
-    <t>["columns-feature","columns-feature","cards-media"]</t>
-  </si>
-  <si>
-    <t>blog</t>
-  </si>
-  <si>
-    <t>article-index</t>
-  </si>
-  <si>
-    <t>2026-09-03T05:19:03.131Z</t>
-  </si>
-  <si>
-    <t>Blog — WKND Trendsetters</t>
-  </si>
-  <si>
-    <t>https://wknd-trendsetters.site/blog</t>
-  </si>
-  <si>
-    <t>case-studies.report.json</t>
-  </si>
-  <si>
-    <t>["columns-feature","columns-feature"]</t>
-  </si>
-  <si>
-    <t>case-studies</t>
-  </si>
-  <si>
-    <t>2026-09-03T06:16:05.414Z</t>
-  </si>
-  <si>
-    <t>Inspiring Case Studies | Fashion Blog</t>
-  </si>
-  <si>
-    <t>https://wknd-trendsetters.site/case-studies</t>
-  </si>
-  <si>
-    <t>faq.report.json</t>
-  </si>
-  <si>
-    <t>["columns-feature","columns-feature","accordion-faq"]</t>
-  </si>
-  <si>
-    <t>faq</t>
-  </si>
-  <si>
-    <t>2026-09-03T06:19:37.928Z</t>
-  </si>
-  <si>
-    <t>FAQ - The Fashion Blog</t>
-  </si>
-  <si>
-    <t>https://wknd-trendsetters.site/faq</t>
-  </si>
-  <si>
-    <t>fashion-insights.report.json</t>
-  </si>
-  <si>
-    <t>fashion-insights</t>
-  </si>
-  <si>
-    <t>2026-09-03T06:16:09.229Z</t>
-  </si>
-  <si>
-    <t>Fashion Blog - Discover Trends in Young Fashion</t>
-  </si>
-  <si>
-    <t>https://wknd-trendsetters.site/fashion-insights</t>
-  </si>
-  <si>
-    <t>fashion-trends-of-the-season.report.json</t>
-  </si>
-  <si>
-    <t>["columns-feature"]</t>
-  </si>
-  <si>
-    <t>fashion-trends-of-the-season</t>
-  </si>
-  <si>
-    <t>trends-landing</t>
-  </si>
-  <si>
-    <t>2026-09-03T06:15:15.381Z</t>
-  </si>
-  <si>
-    <t>Top Fashion Trends for Young People | Fashion Blog</t>
-  </si>
-  <si>
-    <t>https://wknd-trendsetters.site/fashion-trends-of-the-season</t>
-  </si>
-  <si>
-    <t>fashion-trends-young-adults-casual-sport.report.json</t>
-  </si>
-  <si>
-    <t>fashion-trends-young-adults-casual-sport</t>
-  </si>
-  <si>
-    <t>2026-09-02T18:07:04.572Z</t>
-  </si>
-  <si>
-    <t>Fashion Trends for Young Adults | Fashion Blog</t>
-  </si>
-  <si>
-    <t>https://wknd-trendsetters.site/fashion-trends-young-adults-casual-sport</t>
-  </si>
-  <si>
-    <t>fashion-trends-young-adults.report.json</t>
-  </si>
-  <si>
-    <t>["columns-feature","cards-media","cards-media","cards-media"]</t>
-  </si>
-  <si>
-    <t>fashion-trends-young-adults</t>
-  </si>
-  <si>
-    <t>2026-09-03T05:46:00.231Z</t>
-  </si>
-  <si>
-    <t>Fashion Trends for Young Adults - Fashion Blog</t>
-  </si>
-  <si>
-    <t>https://wknd-trendsetters.site/fashion-trends-young-adults</t>
-  </si>
-  <si>
-    <t>index.report.json</t>
-  </si>
-  <si>
-    <t>index</t>
-  </si>
-  <si>
-    <t>2026-09-03T06:15:09.529Z</t>
-  </si>
-  <si>
-    <t>https://wknd-trendsetters.site/</t>
-  </si>
-  <si>
-    <t>blog/ace-pro-court-polo.report.json</t>
-  </si>
-  <si>
-    <t>["columns-article","table-spec"]</t>
-  </si>
-  <si>
-    <t>blog/ace-pro-court-polo</t>
-  </si>
-  <si>
-    <t>2026-09-02T08:57:44.303Z</t>
-  </si>
-  <si>
-    <t>Court cool, street ready — the Ace Pro polo | Fashion Blog</t>
-  </si>
-  <si>
-    <t>https://wknd-trendsetters.site/blog/ace-pro-court-polo</t>
-  </si>
-  <si>
-    <t>blog/fashion-blog-post.report.json</t>
-  </si>
-  <si>
-    <t>["columns-article"]</t>
-  </si>
-  <si>
-    <t>blog/fashion-blog-post</t>
-  </si>
-  <si>
-    <t>2026-09-02T17:33:14.871Z</t>
-  </si>
-  <si>
-    <t>Game on, style up | Fashion Blog</t>
-  </si>
-  <si>
-    <t>https://wknd-trendsetters.site/blog/fashion-blog-post</t>
-  </si>
-  <si>
-    <t>blog/fashion-trends-young-culture.report.json</t>
-  </si>
-  <si>
-    <t>blog/fashion-trends-young-culture</t>
-  </si>
-  <si>
-    <t>2026-09-02T17:33:05.631Z</t>
-  </si>
-  <si>
-    <t>Sunkissed and effortless | Fashion Blog</t>
-  </si>
-  <si>
-    <t>https://wknd-trendsetters.site/blog/fashion-trends-young-culture</t>
-  </si>
-  <si>
-    <t>blog/fashion-trends-young-style.report.json</t>
-  </si>
-  <si>
-    <t>blog/fashion-trends-young-style</t>
-  </si>
-  <si>
-    <t>2026-09-02T17:33:10.033Z</t>
-  </si>
-  <si>
-    <t>Party fits that pop | Fashion Blog</t>
-  </si>
-  <si>
-    <t>https://wknd-trendsetters.site/blog/fashion-trends-young-style</t>
-  </si>
-  <si>
-    <t>blog/flip-flop-summer-style.report.json</t>
-  </si>
-  <si>
-    <t>blog/flip-flop-summer-style</t>
-  </si>
-  <si>
-    <t>2026-09-02T17:32:56.858Z</t>
-  </si>
-  <si>
-    <t>Slide into summer — flip flops that serve | Fashion Blog</t>
-  </si>
-  <si>
-    <t>https://wknd-trendsetters.site/blog/flip-flop-summer-style</t>
-  </si>
-  <si>
-    <t>blog/latest-trends-young-casual-fashion.report.json</t>
-  </si>
-  <si>
-    <t>blog/latest-trends-young-casual-fashion</t>
-  </si>
-  <si>
-    <t>2026-09-02T17:33:01.572Z</t>
-  </si>
-  <si>
-    <t>Tennis style, redefined | Fashion Blog</t>
-  </si>
-  <si>
-    <t>https://wknd-trendsetters.site/blog/latest-trends-young-casual-fashion</t>
-  </si>
-  <si>
-    <t>blog/street-style-trends.report.json</t>
-  </si>
-  <si>
-    <t>blog/street-style-trends</t>
-  </si>
-  <si>
-    <t>2026-09-02T17:33:19.128Z</t>
-  </si>
-  <si>
-    <t>Street style, your way | Fashion Blog</t>
-  </si>
-  <si>
-    <t>https://wknd-trendsetters.site/blog/street-style-trends</t>
-  </si>
-  <si>
-    <t>magazine/article-1.report.json</t>
-  </si>
-  <si>
-    <t>magazine/article-1</t>
-  </si>
-  <si>
-    <t>2026-09-02T06:50:43.262Z</t>
   </si>
   <si>
     <t>https://wknd-trendsetters.site/magazine/article-1</t>
@@ -705,17 +720,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="8" width="50" customWidth="1"/>
+    <col min="1" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="10" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -740,146 +755,182 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="H6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -888,303 +939,375 @@
         <v>42</v>
       </c>
       <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>44</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="G8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" t="s">
         <v>49</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" t="s">
         <v>55</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H10" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" t="s">
+        <v>11</v>
+      </c>
+      <c r="J10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s">
         <v>65</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s">
         <v>69</v>
       </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" t="s">
-        <v>71</v>
-      </c>
-      <c r="H12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" t="s">
-        <v>68</v>
-      </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
         <v>76</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="F14" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="G14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" t="s">
         <v>81</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="F15" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="G15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" t="s">
         <v>86</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="F16" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="G16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" t="s">
         <v>91</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="F17" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="G17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" t="s">
         <v>96</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="F18" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="I18" t="s">
+        <v>103</v>
+      </c>
+      <c r="J18" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
